--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -910,7 +910,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="90">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1674,7 +1674,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -2052,56 +2052,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2419,6 +2374,18 @@
     <xf numFmtId="0" fontId="1" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2446,6 +2413,24 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2500,24 +2485,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2525,51 +2492,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3024,18 +2946,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="111" t="s">
+      <c r="H9" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="112"/>
-      <c r="P9" s="112"/>
-      <c r="Q9" s="113"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="116"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="116"/>
+      <c r="P9" s="116"/>
+      <c r="Q9" s="117"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -3304,11 +3226,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="114" t="s">
+      <c r="H22" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="115"/>
-      <c r="J22" s="116"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="120"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -3385,39 +3307,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="117" t="s">
+      <c r="H9" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="118"/>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118"/>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118"/>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118"/>
-      <c r="AA9" s="118"/>
-      <c r="AB9" s="118"/>
-      <c r="AC9" s="118"/>
-      <c r="AD9" s="118"/>
-      <c r="AE9" s="118"/>
-      <c r="AF9" s="118"/>
-      <c r="AG9" s="118"/>
-      <c r="AH9" s="118"/>
-      <c r="AI9" s="118"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="118"/>
-      <c r="AL9" s="118"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="122"/>
+      <c r="P9" s="122"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="122"/>
+      <c r="S9" s="122"/>
+      <c r="T9" s="122"/>
+      <c r="U9" s="122"/>
+      <c r="V9" s="122"/>
+      <c r="W9" s="122"/>
+      <c r="X9" s="122"/>
+      <c r="Y9" s="122"/>
+      <c r="Z9" s="122"/>
+      <c r="AA9" s="122"/>
+      <c r="AB9" s="122"/>
+      <c r="AC9" s="122"/>
+      <c r="AD9" s="122"/>
+      <c r="AE9" s="122"/>
+      <c r="AF9" s="122"/>
+      <c r="AG9" s="122"/>
+      <c r="AH9" s="122"/>
+      <c r="AI9" s="122"/>
+      <c r="AJ9" s="122"/>
+      <c r="AK9" s="122"/>
+      <c r="AL9" s="122"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -5097,11 +5019,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="119" t="s">
+      <c r="H42" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="119"/>
-      <c r="J42" s="119"/>
+      <c r="I42" s="123"/>
+      <c r="J42" s="123"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -5266,66 +5188,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="125"/>
-      <c r="B1" s="126"/>
-      <c r="C1" s="127"/>
+      <c r="A1" s="135"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="131" t="s">
+      <c r="E1" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="132" t="s">
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="133" t="s">
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="133"/>
-      <c r="U1" s="134" t="s">
+      <c r="T1" s="143"/>
+      <c r="U1" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="137" t="s">
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="120" t="s">
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="121" t="s">
+      <c r="AF1" s="130"/>
+      <c r="AG1" s="130"/>
+      <c r="AH1" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="121"/>
-      <c r="AK1" s="122" t="s">
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="132" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="128"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="130"/>
+      <c r="A2" s="138"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5419,7 +5341,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="123"/>
+      <c r="AK2" s="133"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5530,7 +5452,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="124"/>
+      <c r="AK3" s="134"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -7581,12 +7503,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="141" t="s">
+      <c r="A35" s="127" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="142"/>
-      <c r="C35" s="142"/>
-      <c r="D35" s="143"/>
+      <c r="B35" s="128"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="129"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7718,84 +7640,84 @@
       <c r="AK35" s="25"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="138" t="s">
+      <c r="AG36" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="139"/>
-      <c r="AI36" s="139"/>
-      <c r="AJ36" s="140"/>
+      <c r="AH36" s="125"/>
+      <c r="AI36" s="125"/>
+      <c r="AJ36" s="126"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="138" t="s">
+      <c r="AG37" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="139"/>
-      <c r="AI37" s="139"/>
-      <c r="AJ37" s="140"/>
+      <c r="AH37" s="125"/>
+      <c r="AI37" s="125"/>
+      <c r="AJ37" s="126"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="138" t="s">
+      <c r="AG38" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="139"/>
-      <c r="AI38" s="139"/>
-      <c r="AJ38" s="140"/>
+      <c r="AH38" s="125"/>
+      <c r="AI38" s="125"/>
+      <c r="AJ38" s="126"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="138" t="s">
+      <c r="AG39" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="139"/>
-      <c r="AI39" s="139"/>
-      <c r="AJ39" s="140"/>
+      <c r="AH39" s="125"/>
+      <c r="AI39" s="125"/>
+      <c r="AJ39" s="126"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="138" t="s">
+      <c r="AG40" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="139"/>
-      <c r="AI40" s="139"/>
-      <c r="AJ40" s="140"/>
+      <c r="AH40" s="125"/>
+      <c r="AI40" s="125"/>
+      <c r="AJ40" s="126"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="138" t="s">
+      <c r="AG41" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="139"/>
-      <c r="AI41" s="139"/>
-      <c r="AJ41" s="140"/>
+      <c r="AH41" s="125"/>
+      <c r="AI41" s="125"/>
+      <c r="AJ41" s="126"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="138" t="s">
+      <c r="AG42" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="139"/>
-      <c r="AI42" s="139"/>
-      <c r="AJ42" s="140"/>
+      <c r="AH42" s="125"/>
+      <c r="AI42" s="125"/>
+      <c r="AJ42" s="126"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
@@ -7806,14 +7728,6 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7823,6 +7737,14 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
     <cfRule type="expression" dxfId="12" priority="7">
@@ -7900,66 +7822,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="125"/>
-      <c r="B1" s="126"/>
-      <c r="C1" s="127"/>
+      <c r="A1" s="135"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="131" t="s">
+      <c r="E1" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="132" t="s">
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="144" t="s">
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="145"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="134" t="s">
+      <c r="S1" s="149"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="137" t="s">
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="120" t="s">
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="121" t="s">
+      <c r="AF1" s="130"/>
+      <c r="AG1" s="130"/>
+      <c r="AH1" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="121"/>
-      <c r="AK1" s="122" t="s">
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="132" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="128"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="130"/>
+      <c r="A2" s="138"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -8053,7 +7975,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="123"/>
+      <c r="AK2" s="133"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -8164,7 +8086,7 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="124"/>
+      <c r="AK3" s="134"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -8488,14 +8410,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="15.75" thickBot="1">
+    <row r="9" spans="1:37">
       <c r="A9" s="69">
         <v>6</v>
       </c>
-      <c r="B9" s="147" t="s">
+      <c r="B9" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="148">
+      <c r="C9" s="112">
         <v>46271</v>
       </c>
       <c r="D9" s="69" t="s">
@@ -8522,9 +8444,9 @@
       <c r="O9" s="71"/>
       <c r="P9" s="71"/>
       <c r="Q9" s="71"/>
-      <c r="R9" s="149"/>
-      <c r="S9" s="149"/>
-      <c r="T9" s="149"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="113"/>
       <c r="U9" s="73"/>
       <c r="V9" s="73"/>
       <c r="W9" s="73"/>
@@ -8556,66 +8478,68 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A10" s="151">
+    <row r="10" spans="1:37">
+      <c r="A10" s="30">
         <v>7</v>
       </c>
-      <c r="B10" s="152" t="s">
+      <c r="B10" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="153">
+      <c r="C10" s="22">
         <v>46272</v>
       </c>
-      <c r="D10" s="152" t="s">
+      <c r="D10" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="154" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="154"/>
-      <c r="I10" s="154"/>
-      <c r="J10" s="154"/>
-      <c r="K10" s="154"/>
-      <c r="L10" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="M10" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="N10" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="O10" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="P10" s="155"/>
-      <c r="Q10" s="155"/>
-      <c r="R10" s="156"/>
-      <c r="S10" s="156"/>
-      <c r="T10" s="156"/>
-      <c r="U10" s="157"/>
-      <c r="V10" s="157"/>
-      <c r="W10" s="157"/>
-      <c r="X10" s="157"/>
-      <c r="Y10" s="157"/>
-      <c r="Z10" s="158"/>
-      <c r="AA10" s="158"/>
-      <c r="AB10" s="158"/>
-      <c r="AC10" s="158"/>
-      <c r="AD10" s="158"/>
-      <c r="AE10" s="159"/>
-      <c r="AF10" s="159" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG10" s="159"/>
-      <c r="AH10" s="160"/>
-      <c r="AI10" s="160"/>
-      <c r="AJ10" s="160"/>
-      <c r="AK10" s="161">
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="65"/>
+      <c r="AE10" s="66"/>
+      <c r="AF10" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG10" s="66"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="67"/>
+      <c r="AK10" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -8625,22 +8549,32 @@
       <c r="B11" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="150">
+      <c r="C11" s="114">
         <v>46273</v>
       </c>
-      <c r="D11" s="84"/>
+      <c r="D11" s="84" t="s">
+        <v>62</v>
+      </c>
       <c r="E11" s="77"/>
       <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
+      <c r="G11" s="77" t="s">
+        <v>12</v>
+      </c>
       <c r="H11" s="77"/>
       <c r="I11" s="77"/>
       <c r="J11" s="77"/>
       <c r="K11" s="77"/>
-      <c r="L11" s="78"/>
+      <c r="L11" s="78" t="s">
+        <v>12</v>
+      </c>
       <c r="M11" s="78"/>
-      <c r="N11" s="78"/>
+      <c r="N11" s="78" t="s">
+        <v>12</v>
+      </c>
       <c r="O11" s="78"/>
-      <c r="P11" s="78"/>
+      <c r="P11" s="78" t="s">
+        <v>12</v>
+      </c>
       <c r="Q11" s="78"/>
       <c r="R11" s="79"/>
       <c r="S11" s="79"/>
@@ -8654,7 +8588,9 @@
       <c r="AA11" s="81"/>
       <c r="AB11" s="81"/>
       <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
+      <c r="AD11" s="81" t="s">
+        <v>12</v>
+      </c>
       <c r="AE11" s="82"/>
       <c r="AF11" s="82"/>
       <c r="AG11" s="82"/>
@@ -8663,7 +8599,7 @@
       <c r="AJ11" s="83"/>
       <c r="AK11" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -8676,32 +8612,48 @@
       <c r="C12" s="22">
         <v>46274</v>
       </c>
-      <c r="D12" s="30"/>
+      <c r="D12" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E12" s="62"/>
       <c r="F12" s="62"/>
       <c r="G12" s="62"/>
       <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
+      <c r="I12" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="J12" s="62"/>
       <c r="K12" s="62"/>
-      <c r="L12" s="63"/>
+      <c r="L12" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="M12" s="63"/>
-      <c r="N12" s="63"/>
+      <c r="N12" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="O12" s="63"/>
-      <c r="P12" s="63"/>
+      <c r="P12" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="Q12" s="63"/>
       <c r="R12" s="28"/>
       <c r="S12" s="28"/>
       <c r="T12" s="28"/>
-      <c r="U12" s="64"/>
+      <c r="U12" s="64" t="s">
+        <v>12</v>
+      </c>
       <c r="V12" s="64"/>
       <c r="W12" s="64"/>
-      <c r="X12" s="64"/>
+      <c r="X12" s="64" t="s">
+        <v>12</v>
+      </c>
       <c r="Y12" s="64"/>
       <c r="Z12" s="65"/>
       <c r="AA12" s="65"/>
       <c r="AB12" s="65"/>
-      <c r="AC12" s="65"/>
+      <c r="AC12" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AD12" s="65"/>
       <c r="AE12" s="66"/>
       <c r="AF12" s="66"/>
@@ -8711,7 +8663,7 @@
       <c r="AJ12" s="67"/>
       <c r="AK12" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -8724,7 +8676,9 @@
       <c r="C13" s="22">
         <v>46275</v>
       </c>
-      <c r="D13" s="30"/>
+      <c r="D13" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E13" s="62"/>
       <c r="F13" s="62"/>
       <c r="G13" s="62"/>
@@ -8733,10 +8687,16 @@
       <c r="J13" s="62"/>
       <c r="K13" s="62"/>
       <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="63"/>
+      <c r="M13" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="O13" s="63"/>
-      <c r="P13" s="63"/>
+      <c r="P13" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="Q13" s="63"/>
       <c r="R13" s="29"/>
       <c r="S13" s="29"/>
@@ -8759,7 +8719,7 @@
       <c r="AJ13" s="67"/>
       <c r="AK13" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -9723,12 +9683,12 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="141" t="s">
+      <c r="A34" s="127" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="142"/>
-      <c r="C34" s="142"/>
-      <c r="D34" s="143"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="128"/>
+      <c r="D34" s="129"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>1</v>
@@ -9739,7 +9699,7 @@
       </c>
       <c r="G34" s="106">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H34" s="106">
         <f t="shared" si="1"/>
@@ -9747,7 +9707,7 @@
       </c>
       <c r="I34" s="106">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" s="106">
         <f t="shared" si="1"/>
@@ -9759,15 +9719,15 @@
       </c>
       <c r="L34" s="63">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M34" s="63">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N34" s="63">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O34" s="63">
         <f t="shared" si="1"/>
@@ -9775,7 +9735,7 @@
       </c>
       <c r="P34" s="63">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q34" s="63">
         <f t="shared" si="1"/>
@@ -9795,7 +9755,7 @@
       </c>
       <c r="U34" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="64">
         <f t="shared" si="1"/>
@@ -9807,7 +9767,7 @@
       </c>
       <c r="X34" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="64">
         <f t="shared" si="1"/>
@@ -9823,15 +9783,15 @@
       </c>
       <c r="AB34" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC34" s="65">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD34" s="65">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE34" s="66">
         <f t="shared" si="1"/>
@@ -9860,84 +9820,84 @@
       <c r="AK34" s="25"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="138" t="s">
+      <c r="AG35" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="139"/>
-      <c r="AI35" s="139"/>
-      <c r="AJ35" s="140"/>
+      <c r="AH35" s="125"/>
+      <c r="AI35" s="125"/>
+      <c r="AJ35" s="126"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="138" t="s">
+      <c r="AG36" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="139"/>
-      <c r="AI36" s="139"/>
-      <c r="AJ36" s="140"/>
+      <c r="AH36" s="125"/>
+      <c r="AI36" s="125"/>
+      <c r="AJ36" s="126"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="138" t="s">
+      <c r="AG37" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="139"/>
-      <c r="AI37" s="139"/>
-      <c r="AJ37" s="140"/>
+      <c r="AH37" s="125"/>
+      <c r="AI37" s="125"/>
+      <c r="AJ37" s="126"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="138" t="s">
+      <c r="AG38" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="139"/>
-      <c r="AI38" s="139"/>
-      <c r="AJ38" s="140"/>
+      <c r="AH38" s="125"/>
+      <c r="AI38" s="125"/>
+      <c r="AJ38" s="126"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="138" t="s">
+      <c r="AG39" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="139"/>
-      <c r="AI39" s="139"/>
-      <c r="AJ39" s="140"/>
+      <c r="AH39" s="125"/>
+      <c r="AI39" s="125"/>
+      <c r="AJ39" s="126"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="138" t="s">
+      <c r="AG40" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="139"/>
-      <c r="AI40" s="139"/>
-      <c r="AJ40" s="140"/>
+      <c r="AH40" s="125"/>
+      <c r="AI40" s="125"/>
+      <c r="AJ40" s="126"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="138" t="s">
+      <c r="AG41" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="139"/>
-      <c r="AI41" s="139"/>
-      <c r="AJ41" s="140"/>
+      <c r="AH41" s="125"/>
+      <c r="AI41" s="125"/>
+      <c r="AJ41" s="126"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
@@ -9948,23 +9908,23 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="AG35:AJ35"/>
+    <mergeCell ref="AG36:AJ36"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
-    <mergeCell ref="AG35:AJ35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
     <cfRule type="expression" dxfId="5" priority="7">

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -905,12 +905,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="AI16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Заставил себя сесть и поделать KPI
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="92">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1180,6 +1194,12 @@
   </si>
   <si>
     <t>Упражнения для голоса</t>
+  </si>
+  <si>
+    <t>Таблица Шульте (с 14.09)</t>
+  </si>
+  <si>
+    <t>Заявление в суд и в МТС</t>
   </si>
 </sst>
 </file>
@@ -2413,6 +2433,60 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2429,60 +2503,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5188,66 +5208,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="135"/>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="131"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="142" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="143" t="s">
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="143"/>
-      <c r="U1" s="144" t="s">
+      <c r="T1" s="137"/>
+      <c r="U1" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="146"/>
-      <c r="Z1" s="147" t="s">
+      <c r="V1" s="139"/>
+      <c r="W1" s="139"/>
+      <c r="X1" s="139"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="147"/>
-      <c r="AB1" s="147"/>
-      <c r="AC1" s="147"/>
-      <c r="AD1" s="147"/>
-      <c r="AE1" s="130" t="s">
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="141"/>
+      <c r="AE1" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="130"/>
-      <c r="AH1" s="131" t="s">
+      <c r="AF1" s="124"/>
+      <c r="AG1" s="124"/>
+      <c r="AH1" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="132" t="s">
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="126" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="138"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
+      <c r="A2" s="132"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="134"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5341,7 +5361,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="133"/>
+      <c r="AK2" s="127"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5452,7 +5472,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="134"/>
+      <c r="AK3" s="128"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -7503,12 +7523,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="127" t="s">
+      <c r="A35" s="145" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="128"/>
-      <c r="C35" s="128"/>
-      <c r="D35" s="129"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="147"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7640,84 +7660,84 @@
       <c r="AK35" s="25"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="124" t="s">
+      <c r="AG36" s="142" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="125"/>
-      <c r="AI36" s="125"/>
-      <c r="AJ36" s="126"/>
+      <c r="AH36" s="143"/>
+      <c r="AI36" s="143"/>
+      <c r="AJ36" s="144"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="124" t="s">
+      <c r="AG37" s="142" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="125"/>
-      <c r="AI37" s="125"/>
-      <c r="AJ37" s="126"/>
+      <c r="AH37" s="143"/>
+      <c r="AI37" s="143"/>
+      <c r="AJ37" s="144"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="124" t="s">
+      <c r="AG38" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="125"/>
-      <c r="AI38" s="125"/>
-      <c r="AJ38" s="126"/>
+      <c r="AH38" s="143"/>
+      <c r="AI38" s="143"/>
+      <c r="AJ38" s="144"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="124" t="s">
+      <c r="AG39" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="125"/>
-      <c r="AI39" s="125"/>
-      <c r="AJ39" s="126"/>
+      <c r="AH39" s="143"/>
+      <c r="AI39" s="143"/>
+      <c r="AJ39" s="144"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="124" t="s">
+      <c r="AG40" s="142" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="125"/>
-      <c r="AI40" s="125"/>
-      <c r="AJ40" s="126"/>
+      <c r="AH40" s="143"/>
+      <c r="AI40" s="143"/>
+      <c r="AJ40" s="144"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="124" t="s">
+      <c r="AG41" s="142" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="125"/>
-      <c r="AI41" s="125"/>
-      <c r="AJ41" s="126"/>
+      <c r="AH41" s="143"/>
+      <c r="AI41" s="143"/>
+      <c r="AJ41" s="144"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="124" t="s">
+      <c r="AG42" s="142" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="125"/>
-      <c r="AI42" s="125"/>
-      <c r="AJ42" s="126"/>
+      <c r="AH42" s="143"/>
+      <c r="AI42" s="143"/>
+      <c r="AJ42" s="144"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
@@ -7728,6 +7748,14 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7737,14 +7765,6 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
     <cfRule type="expression" dxfId="12" priority="7">
@@ -7822,66 +7842,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="135"/>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="131"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="142" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
       <c r="R1" s="148" t="s">
         <v>39</v>
       </c>
       <c r="S1" s="149"/>
       <c r="T1" s="150"/>
-      <c r="U1" s="144" t="s">
+      <c r="U1" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="146"/>
-      <c r="Z1" s="147" t="s">
+      <c r="V1" s="139"/>
+      <c r="W1" s="139"/>
+      <c r="X1" s="139"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="147"/>
-      <c r="AB1" s="147"/>
-      <c r="AC1" s="147"/>
-      <c r="AD1" s="147"/>
-      <c r="AE1" s="130" t="s">
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="141"/>
+      <c r="AE1" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="130"/>
-      <c r="AH1" s="131" t="s">
+      <c r="AF1" s="124"/>
+      <c r="AG1" s="124"/>
+      <c r="AH1" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="132" t="s">
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="126" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="138"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
+      <c r="A2" s="132"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="134"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -7964,7 +7984,7 @@
         <v>60</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AF2" s="11" t="s">
         <v>88</v>
@@ -7972,10 +7992,12 @@
       <c r="AG2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="AH2" s="12"/>
+      <c r="AH2" s="12" t="s">
+        <v>90</v>
+      </c>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="133"/>
+      <c r="AK2" s="127"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -8086,7 +8108,7 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="134"/>
+      <c r="AK3" s="128"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -8732,7 +8754,9 @@
       <c r="C14" s="22">
         <v>46276</v>
       </c>
-      <c r="D14" s="30"/>
+      <c r="D14" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E14" s="62"/>
       <c r="F14" s="62"/>
       <c r="G14" s="62"/>
@@ -8741,10 +8765,18 @@
       <c r="J14" s="62"/>
       <c r="K14" s="62"/>
       <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
+      <c r="M14" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P14" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="Q14" s="63"/>
       <c r="R14" s="29"/>
       <c r="S14" s="29"/>
@@ -8754,11 +8786,17 @@
       <c r="W14" s="64"/>
       <c r="X14" s="64"/>
       <c r="Y14" s="64"/>
-      <c r="Z14" s="65"/>
+      <c r="Z14" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AA14" s="65"/>
-      <c r="AB14" s="65"/>
+      <c r="AB14" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AC14" s="65"/>
-      <c r="AD14" s="65"/>
+      <c r="AD14" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE14" s="66"/>
       <c r="AF14" s="66"/>
       <c r="AG14" s="66"/>
@@ -8767,7 +8805,7 @@
       <c r="AJ14" s="67"/>
       <c r="AK14" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -8780,10 +8818,14 @@
       <c r="C15" s="22">
         <v>46277</v>
       </c>
-      <c r="D15" s="30"/>
+      <c r="D15" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E15" s="62"/>
       <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
+      <c r="G15" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
       <c r="J15" s="62"/>
@@ -8805,8 +8847,12 @@
       <c r="Z15" s="65"/>
       <c r="AA15" s="65"/>
       <c r="AB15" s="65"/>
-      <c r="AC15" s="65"/>
-      <c r="AD15" s="65"/>
+      <c r="AC15" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD15" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE15" s="66"/>
       <c r="AF15" s="66"/>
       <c r="AG15" s="66"/>
@@ -8815,7 +8861,7 @@
       <c r="AJ15" s="67"/>
       <c r="AK15" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -8828,7 +8874,9 @@
       <c r="C16" s="22">
         <v>46278</v>
       </c>
-      <c r="D16" s="69"/>
+      <c r="D16" s="69" t="s">
+        <v>62</v>
+      </c>
       <c r="E16" s="70"/>
       <c r="F16" s="70"/>
       <c r="G16" s="70"/>
@@ -8854,16 +8902,20 @@
       <c r="AA16" s="74"/>
       <c r="AB16" s="74"/>
       <c r="AC16" s="74"/>
-      <c r="AD16" s="74"/>
+      <c r="AD16" s="74" t="s">
+        <v>12</v>
+      </c>
       <c r="AE16" s="75"/>
       <c r="AF16" s="75"/>
       <c r="AG16" s="75"/>
       <c r="AH16" s="76"/>
-      <c r="AI16" s="76"/>
+      <c r="AI16" s="76" t="s">
+        <v>12</v>
+      </c>
       <c r="AJ16" s="76"/>
       <c r="AK16" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -8876,7 +8928,9 @@
       <c r="C17" s="22">
         <v>46279</v>
       </c>
-      <c r="D17" s="69"/>
+      <c r="D17" s="69" t="s">
+        <v>62</v>
+      </c>
       <c r="E17" s="70"/>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
@@ -8884,9 +8938,15 @@
       <c r="I17" s="70"/>
       <c r="J17" s="70"/>
       <c r="K17" s="70"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
+      <c r="L17" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="71" t="s">
+        <v>12</v>
+      </c>
       <c r="O17" s="71"/>
       <c r="P17" s="71"/>
       <c r="Q17" s="71"/>
@@ -8896,22 +8956,28 @@
       <c r="U17" s="73"/>
       <c r="V17" s="73"/>
       <c r="W17" s="73"/>
-      <c r="X17" s="73"/>
+      <c r="X17" s="73" t="s">
+        <v>12</v>
+      </c>
       <c r="Y17" s="73"/>
       <c r="Z17" s="74"/>
       <c r="AA17" s="74"/>
       <c r="AB17" s="74"/>
       <c r="AC17" s="74"/>
-      <c r="AD17" s="74"/>
+      <c r="AD17" s="74" t="s">
+        <v>12</v>
+      </c>
       <c r="AE17" s="75"/>
       <c r="AF17" s="75"/>
       <c r="AG17" s="75"/>
-      <c r="AH17" s="76"/>
+      <c r="AH17" s="76" t="s">
+        <v>12</v>
+      </c>
       <c r="AI17" s="76"/>
       <c r="AJ17" s="76"/>
       <c r="AK17" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -8924,24 +8990,36 @@
       <c r="C18" s="22">
         <v>46280</v>
       </c>
-      <c r="D18" s="30"/>
+      <c r="D18" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E18" s="62"/>
       <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
+      <c r="G18" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H18" s="62"/>
       <c r="I18" s="62"/>
       <c r="J18" s="62"/>
       <c r="K18" s="62"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="63"/>
+      <c r="L18" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N18" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="O18" s="63"/>
       <c r="P18" s="63"/>
       <c r="Q18" s="63"/>
       <c r="R18" s="29"/>
       <c r="S18" s="29"/>
       <c r="T18" s="29"/>
-      <c r="U18" s="64"/>
+      <c r="U18" s="64" t="s">
+        <v>12</v>
+      </c>
       <c r="V18" s="64"/>
       <c r="W18" s="64"/>
       <c r="X18" s="64"/>
@@ -8954,12 +9032,14 @@
       <c r="AE18" s="66"/>
       <c r="AF18" s="66"/>
       <c r="AG18" s="66"/>
-      <c r="AH18" s="67"/>
+      <c r="AH18" s="67" t="s">
+        <v>12</v>
+      </c>
       <c r="AI18" s="67"/>
       <c r="AJ18" s="67"/>
       <c r="AK18" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -8972,7 +9052,9 @@
       <c r="C19" s="22">
         <v>46281</v>
       </c>
-      <c r="D19" s="85"/>
+      <c r="D19" s="85" t="s">
+        <v>62</v>
+      </c>
       <c r="E19" s="86"/>
       <c r="F19" s="86"/>
       <c r="G19" s="86"/>
@@ -8980,9 +9062,15 @@
       <c r="I19" s="86"/>
       <c r="J19" s="86"/>
       <c r="K19" s="86"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="87"/>
-      <c r="N19" s="87"/>
+      <c r="L19" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="N19" s="87" t="s">
+        <v>12</v>
+      </c>
       <c r="O19" s="87"/>
       <c r="P19" s="87"/>
       <c r="Q19" s="87"/>
@@ -8992,22 +9080,28 @@
       <c r="U19" s="89"/>
       <c r="V19" s="89"/>
       <c r="W19" s="89"/>
-      <c r="X19" s="89"/>
+      <c r="X19" s="89" t="s">
+        <v>12</v>
+      </c>
       <c r="Y19" s="89"/>
       <c r="Z19" s="90"/>
-      <c r="AA19" s="90"/>
+      <c r="AA19" s="90" t="s">
+        <v>12</v>
+      </c>
       <c r="AB19" s="90"/>
       <c r="AC19" s="90"/>
       <c r="AD19" s="90"/>
       <c r="AE19" s="91"/>
       <c r="AF19" s="91"/>
       <c r="AG19" s="91"/>
-      <c r="AH19" s="92"/>
+      <c r="AH19" s="92" t="s">
+        <v>12</v>
+      </c>
       <c r="AI19" s="92"/>
       <c r="AJ19" s="92"/>
       <c r="AK19" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -9023,14 +9117,26 @@
       <c r="D20" s="69"/>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
+      <c r="G20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="70" t="s">
+        <v>12</v>
+      </c>
       <c r="J20" s="70"/>
       <c r="K20" s="70"/>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
+      <c r="L20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" s="71" t="s">
+        <v>12</v>
+      </c>
       <c r="O20" s="71"/>
       <c r="P20" s="71"/>
       <c r="Q20" s="71"/>
@@ -9040,22 +9146,30 @@
       <c r="U20" s="73"/>
       <c r="V20" s="73"/>
       <c r="W20" s="73"/>
-      <c r="X20" s="73"/>
+      <c r="X20" s="73" t="s">
+        <v>12</v>
+      </c>
       <c r="Y20" s="73"/>
       <c r="Z20" s="74"/>
       <c r="AA20" s="74"/>
       <c r="AB20" s="74"/>
-      <c r="AC20" s="74"/>
-      <c r="AD20" s="74"/>
+      <c r="AC20" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD20" s="74" t="s">
+        <v>12</v>
+      </c>
       <c r="AE20" s="75"/>
       <c r="AF20" s="75"/>
       <c r="AG20" s="75"/>
-      <c r="AH20" s="76"/>
+      <c r="AH20" s="76" t="s">
+        <v>12</v>
+      </c>
       <c r="AI20" s="76"/>
       <c r="AJ20" s="76"/>
       <c r="AK20" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -9068,17 +9182,31 @@
       <c r="C21" s="22">
         <v>46283</v>
       </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
+      <c r="D21" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="70" t="s">
+        <v>12</v>
+      </c>
       <c r="I21" s="70"/>
       <c r="J21" s="70"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
+      <c r="M21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N21" s="71" t="s">
+        <v>12</v>
+      </c>
       <c r="O21" s="71"/>
       <c r="P21" s="71"/>
       <c r="Q21" s="71"/>
@@ -9103,7 +9231,7 @@
       <c r="AJ21" s="76"/>
       <c r="AK21" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -9683,31 +9811,31 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="145" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="128"/>
-      <c r="C34" s="128"/>
-      <c r="D34" s="129"/>
+      <c r="B34" s="146"/>
+      <c r="C34" s="146"/>
+      <c r="D34" s="147"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="106">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="106">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H34" s="106">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" s="106">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" s="106">
         <f t="shared" si="1"/>
@@ -9719,23 +9847,23 @@
       </c>
       <c r="L34" s="63">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M34" s="63">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N34" s="63">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O34" s="63">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P34" s="63">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q34" s="63">
         <f t="shared" si="1"/>
@@ -9755,7 +9883,7 @@
       </c>
       <c r="U34" s="64">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V34" s="64">
         <f t="shared" si="1"/>
@@ -9767,7 +9895,7 @@
       </c>
       <c r="X34" s="64">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y34" s="64">
         <f t="shared" si="1"/>
@@ -9775,23 +9903,23 @@
       </c>
       <c r="Z34" s="65">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA34" s="65">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB34" s="65">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC34" s="65">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD34" s="65">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE34" s="66">
         <f t="shared" si="1"/>
@@ -9807,11 +9935,11 @@
       </c>
       <c r="AH34" s="67">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI34" s="67">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ34" s="67">
         <f t="shared" si="1"/>
@@ -9820,84 +9948,84 @@
       <c r="AK34" s="25"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="124" t="s">
+      <c r="AG35" s="142" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="125"/>
-      <c r="AI35" s="125"/>
-      <c r="AJ35" s="126"/>
+      <c r="AH35" s="143"/>
+      <c r="AI35" s="143"/>
+      <c r="AJ35" s="144"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="124" t="s">
+      <c r="AG36" s="142" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="125"/>
-      <c r="AI36" s="125"/>
-      <c r="AJ36" s="126"/>
+      <c r="AH36" s="143"/>
+      <c r="AI36" s="143"/>
+      <c r="AJ36" s="144"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="124" t="s">
+      <c r="AG37" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="125"/>
-      <c r="AI37" s="125"/>
-      <c r="AJ37" s="126"/>
+      <c r="AH37" s="143"/>
+      <c r="AI37" s="143"/>
+      <c r="AJ37" s="144"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="124" t="s">
+      <c r="AG38" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="125"/>
-      <c r="AI38" s="125"/>
-      <c r="AJ38" s="126"/>
+      <c r="AH38" s="143"/>
+      <c r="AI38" s="143"/>
+      <c r="AJ38" s="144"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="124" t="s">
+      <c r="AG39" s="142" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="125"/>
-      <c r="AI39" s="125"/>
-      <c r="AJ39" s="126"/>
+      <c r="AH39" s="143"/>
+      <c r="AI39" s="143"/>
+      <c r="AJ39" s="144"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="124" t="s">
+      <c r="AG40" s="142" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="125"/>
-      <c r="AI40" s="125"/>
-      <c r="AJ40" s="126"/>
+      <c r="AH40" s="143"/>
+      <c r="AI40" s="143"/>
+      <c r="AJ40" s="144"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="124" t="s">
+      <c r="AG41" s="142" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="125"/>
-      <c r="AI41" s="125"/>
-      <c r="AJ41" s="126"/>
+      <c r="AH41" s="143"/>
+      <c r="AI41" s="143"/>
+      <c r="AJ41" s="144"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
@@ -9908,23 +10036,23 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="AG37:AJ37"/>
     <mergeCell ref="AG38:AJ38"/>
     <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AG35:AJ35"/>
     <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
     <cfRule type="expression" dxfId="5" priority="7">
